--- a/carreras.xlsx
+++ b/carreras.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\Pagina Ferias\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\Web Ferias\Pagina-Ferias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F624E6B9-ACE7-41EC-8F7B-0E4DD0795729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D264221-2FFD-4692-9F17-2248549E64CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="924" yWindow="4567" windowWidth="16270" windowHeight="5997" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -207,9 +207,6 @@
     <t>$38,220,000</t>
   </si>
   <si>
-    <t>preguntas frecuentes</t>
-  </si>
-  <si>
     <t>Si te gustan las Finanzas, Administración te da la base gerencial y puedes hacer una Opción en Finanzas (que son unas materias extra). Si te gusta el Marketing, aquí aprendes la estrategia detrás del negocio, y puedes profundizar con electivas de comportamiento del consumidor o analítica de datos.</t>
   </si>
   <si>
@@ -637,6 +634,9 @@
   </si>
   <si>
     <t>Beca Decidí Enseñar &amp; Beca Quiero Enseñar (escasos recursos)</t>
+  </si>
+  <si>
+    <t>preguntas_frecuentes</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +1022,7 @@
     <col min="10" max="10" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27.95" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1033,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>59</v>
+        <v>202</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>2</v>
@@ -1048,10 +1048,10 @@
         <v>15</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="139.69999999999999" x14ac:dyDescent="0.3">
@@ -1062,10 +1062,10 @@
         <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>18</v>
@@ -1074,14 +1074,14 @@
         <v>6</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H2" s="3">
         <v>320</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="167.65" x14ac:dyDescent="0.3">
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="F3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H3" s="3">
         <v>310</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="55.9" x14ac:dyDescent="0.3">
@@ -1130,16 +1130,16 @@
         <v>6</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H4" s="3">
         <v>310</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="55.9" x14ac:dyDescent="0.3">
@@ -1159,13 +1159,13 @@
         <v>6</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H5" s="3">
         <v>310</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="55.9" x14ac:dyDescent="0.3">
@@ -1176,25 +1176,25 @@
         <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="F6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H6" s="3">
         <v>310</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="41.95" x14ac:dyDescent="0.3">
@@ -1205,25 +1205,25 @@
         <v>31</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="F7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H7" s="3">
         <v>310</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="55.9" x14ac:dyDescent="0.3">
@@ -1234,25 +1234,25 @@
         <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="F8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H8" s="3">
         <v>310</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="83.85" x14ac:dyDescent="0.3">
@@ -1263,13 +1263,13 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>8</v>
@@ -1281,7 +1281,7 @@
         <v>355</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="41.95" x14ac:dyDescent="0.3">
@@ -1292,25 +1292,25 @@
         <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="F10" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H10" s="3">
         <v>310</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="41.95" x14ac:dyDescent="0.3">
@@ -1321,22 +1321,22 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H11" s="3">
         <v>300</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="209.55" x14ac:dyDescent="0.3">
@@ -1347,10 +1347,10 @@
         <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1359,13 +1359,13 @@
         <v>6</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H12" s="3">
         <v>300</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="41.95" x14ac:dyDescent="0.3">
@@ -1376,25 +1376,25 @@
         <v>34</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H13" s="3">
         <v>300</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="41.95" x14ac:dyDescent="0.3">
@@ -1405,22 +1405,22 @@
         <v>35</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H14" s="3">
         <v>300</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="41.95" x14ac:dyDescent="0.3">
@@ -1431,25 +1431,25 @@
         <v>36</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H15" s="3">
         <v>300</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="41.95" x14ac:dyDescent="0.3">
@@ -1460,25 +1460,25 @@
         <v>37</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H16" s="3">
         <v>300</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="41.95" x14ac:dyDescent="0.3">
@@ -1489,28 +1489,28 @@
         <v>38</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H17" s="3">
         <v>300</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="41.95" x14ac:dyDescent="0.3">
@@ -1521,25 +1521,25 @@
         <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="F18" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H18" s="3">
         <v>310</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="41.95" x14ac:dyDescent="0.3">
@@ -1550,22 +1550,22 @@
         <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="F19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H19" s="3">
         <v>310</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="41.95" x14ac:dyDescent="0.3">
@@ -1576,22 +1576,22 @@
         <v>5</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H20" s="3">
         <v>310</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="41.95" x14ac:dyDescent="0.3">
@@ -1602,25 +1602,25 @@
         <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="F21" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H21" s="3">
         <v>310</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="139.69999999999999" x14ac:dyDescent="0.3">
@@ -1631,28 +1631,28 @@
         <v>42</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H22" s="3">
         <v>310</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="41.95" x14ac:dyDescent="0.3">
@@ -1663,22 +1663,22 @@
         <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="F23" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H23" s="3">
         <v>310</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="125.75" x14ac:dyDescent="0.3">
@@ -1689,25 +1689,25 @@
         <v>43</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H24" s="3">
         <v>310</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="55.9" x14ac:dyDescent="0.3">
@@ -1718,25 +1718,25 @@
         <v>44</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="F25" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H25" s="3">
         <v>310</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="55.9" x14ac:dyDescent="0.3">
@@ -1747,22 +1747,22 @@
         <v>45</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="F26" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H26" s="3">
         <v>310</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="55.9" x14ac:dyDescent="0.3">
@@ -1773,22 +1773,22 @@
         <v>12</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H27" s="3">
         <v>300</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="55.9" x14ac:dyDescent="0.3">
@@ -1799,22 +1799,22 @@
         <v>47</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="G28" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H28" s="3">
         <v>300</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="209.55" x14ac:dyDescent="0.3">
@@ -1825,28 +1825,28 @@
         <v>48</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H29" s="3">
         <v>300</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="153.69999999999999" x14ac:dyDescent="0.3">
@@ -1857,28 +1857,28 @@
         <v>49</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H30" s="3">
         <v>300</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="55.9" x14ac:dyDescent="0.3">
@@ -1889,25 +1889,25 @@
         <v>50</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="F31" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H31" s="3">
         <v>300</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="181.65" x14ac:dyDescent="0.3">
@@ -1918,28 +1918,28 @@
         <v>51</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H32" s="3">
         <v>300</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="41.95" x14ac:dyDescent="0.3">
@@ -1950,25 +1950,25 @@
         <v>52</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="F33" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H33" s="3">
         <v>300</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="55.9" x14ac:dyDescent="0.3">
@@ -1979,25 +1979,25 @@
         <v>57</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="F34" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H34" s="3">
         <v>200</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="83.85" x14ac:dyDescent="0.3">
@@ -2008,25 +2008,25 @@
         <v>54</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="F35" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H35" s="3">
         <v>300</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="83.85" x14ac:dyDescent="0.3">
@@ -2037,25 +2037,25 @@
         <v>22</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="F36" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H36" s="3">
         <v>300</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="83.85" x14ac:dyDescent="0.3">
@@ -2066,25 +2066,25 @@
         <v>55</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="F37" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H37" s="3">
         <v>300</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="83.85" x14ac:dyDescent="0.3">
@@ -2095,25 +2095,25 @@
         <v>56</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="F38" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H38" s="3">
         <v>300</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="83.85" x14ac:dyDescent="0.3">
@@ -2124,25 +2124,25 @@
         <v>50</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="F39" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H39" s="3">
         <v>300</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="83.85" x14ac:dyDescent="0.3">
@@ -2153,25 +2153,25 @@
         <v>9</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="F40" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H40" s="3">
         <v>300</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="83.85" x14ac:dyDescent="0.3">
@@ -2182,25 +2182,25 @@
         <v>57</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="F41" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H41" s="3">
         <v>300</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="83.85" x14ac:dyDescent="0.3">
@@ -2211,25 +2211,25 @@
         <v>31</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="F42" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H42" s="3">
         <v>300</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="83.85" x14ac:dyDescent="0.3">
@@ -2240,52 +2240,52 @@
         <v>33</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H43" s="3">
         <v>300</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="55.9" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="E44" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="F44" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="G44" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H44" s="3">
         <v>300</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
